--- a/Results/df_mnd_lica_pla_sequential_trial_gap_weighted.xlsx
+++ b/Results/df_mnd_lica_pla_sequential_trial_gap_weighted.xlsx
@@ -475,16 +475,16 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.15</v>
       </c>
       <c r="E2" t="n">
-        <v>0.38</v>
+        <v>0.08</v>
       </c>
       <c r="F2" t="n">
-        <v>0.8</v>
+        <v>0.25</v>
       </c>
       <c r="G2" t="n">
-        <v>0.001759852719477159</v>
+        <v>6.797471731128199e-12</v>
       </c>
     </row>
     <row r="3">
@@ -502,16 +502,16 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.14</v>
       </c>
       <c r="E3" t="n">
-        <v>0.39</v>
+        <v>0.09</v>
       </c>
       <c r="F3" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.23</v>
       </c>
       <c r="G3" t="n">
-        <v>0.002298131159495045</v>
+        <v>3.920859064409318e-15</v>
       </c>
     </row>
     <row r="4">
@@ -529,16 +529,16 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.55</v>
+        <v>0.14</v>
       </c>
       <c r="E4" t="n">
-        <v>0.38</v>
+        <v>0.09</v>
       </c>
       <c r="F4" t="n">
-        <v>0.8</v>
+        <v>0.23</v>
       </c>
       <c r="G4" t="n">
-        <v>0.001474944204588464</v>
+        <v>4.694714972482191e-15</v>
       </c>
     </row>
     <row r="5">
@@ -556,16 +556,16 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.05</v>
       </c>
       <c r="E5" t="n">
         <v>0.02</v>
       </c>
       <c r="F5" t="n">
-        <v>0.22</v>
+        <v>0.14</v>
       </c>
       <c r="G5" t="n">
-        <v>6.761351586087314e-06</v>
+        <v>1.918914956104367e-09</v>
       </c>
     </row>
   </sheetData>
